--- a/src/data/testimonials.xlsx
+++ b/src/data/testimonials.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\h2oontherock8\Projects\alexyaphomes\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B96F15-F6E4-4104-93C5-172511F809A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83AE3091-9CB1-4728-88EC-82B66159C628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9580" yWindow="2900" windowWidth="26980" windowHeight="17510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8460" yWindow="2710" windowWidth="30690" windowHeight="17510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Testimonials" sheetId="1" r:id="rId1"/>
@@ -465,11 +465,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -494,14 +491,8 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -519,6 +510,24 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -829,1137 +838,1137 @@
   <dimension ref="A1:K34"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="6.6328125" customWidth="1"/>
     <col min="2" max="2" width="20.54296875" customWidth="1"/>
     <col min="3" max="3" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.26953125" customWidth="1"/>
-    <col min="5" max="5" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="40" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.54296875" customWidth="1"/>
+    <col min="5" max="5" width="14.6328125" customWidth="1"/>
+    <col min="6" max="6" width="34.1796875" customWidth="1"/>
     <col min="7" max="7" width="80.90625" customWidth="1"/>
     <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="8.81640625" customWidth="1"/>
-    <col min="10" max="10" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="2.54296875" customWidth="1"/>
+    <col min="9" max="10" width="9.1796875" customWidth="1"/>
+    <col min="11" max="11" width="2.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="K1" s="18"/>
+      <c r="K1" s="15"/>
     </row>
     <row r="2" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="15">
+      <c r="A2" s="12">
         <f>MAX(A3:A$34) + 1</f>
         <v>32</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="9" t="str">
-        <f>IF(I2="YES", COUNTIF($I$2:I2, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I2, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="J2" s="8" t="str">
+        <f>IF(I2="YES", COUNTIF($I$2:I2, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I2, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
         <v>1st</v>
       </c>
-      <c r="K2" s="18"/>
+      <c r="K2" s="15"/>
     </row>
     <row r="3" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="16">
+      <c r="A3" s="13">
         <f>MAX(A4:A$34) + 1</f>
         <v>31</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="5" t="str">
-        <f>IF(I3="YES", COUNTIF($I$2:I3, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I3, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="J3" s="4" t="str">
+        <f>IF(I3="YES", COUNTIF($I$2:I3, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I3, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
         <v>2nd</v>
       </c>
-      <c r="K3" s="18"/>
+      <c r="K3" s="15"/>
     </row>
     <row r="4" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="15">
+      <c r="A4" s="12">
         <f>MAX(A5:A$34) + 1</f>
         <v>30</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="G4" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="J4" s="9" t="str">
-        <f>IF(I4="YES", COUNTIF($I$2:I4, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I4, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="J4" s="8" t="str">
+        <f>IF(I4="YES", COUNTIF($I$2:I4, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I4, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
         <v>3rd</v>
       </c>
-      <c r="K4" s="18"/>
+      <c r="K4" s="15"/>
     </row>
     <row r="5" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="16">
+      <c r="A5" s="13">
         <f>MAX(A6:A$34) + 1</f>
         <v>29</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="5" t="str">
-        <f>IF(I5="YES", COUNTIF($I$2:I5, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I5, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
-      </c>
-      <c r="K5" s="18"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="4" t="str">
+        <f>IF(I5="YES", COUNTIF($I$2:I5, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I5, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
+      </c>
+      <c r="K5" s="15"/>
     </row>
     <row r="6" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="15">
+      <c r="A6" s="12">
         <f>MAX(A7:A$34) + 1</f>
         <v>28</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="8"/>
-      <c r="J6" s="9" t="str">
-        <f>IF(I6="YES", COUNTIF($I$2:I6, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I6, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
-      </c>
-      <c r="K6" s="18"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="8" t="str">
+        <f>IF(I6="YES", COUNTIF($I$2:I6, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I6, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
+      </c>
+      <c r="K6" s="15"/>
     </row>
     <row r="7" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="16">
+      <c r="A7" s="13">
         <f>MAX(A8:A$34) + 1</f>
         <v>27</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="5" t="str">
-        <f>IF(I7="YES", COUNTIF($I$2:I7, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I7, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
-      </c>
-      <c r="K7" s="18"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="4" t="str">
+        <f>IF(I7="YES", COUNTIF($I$2:I7, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I7, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
+      </c>
+      <c r="K7" s="15"/>
     </row>
     <row r="8" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="15">
+      <c r="A8" s="12">
         <f>MAX(A9:A$34) + 1</f>
         <v>26</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="J8" s="9" t="str">
-        <f>IF(I8="YES", COUNTIF($I$2:I8, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I8, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="J8" s="8" t="str">
+        <f>IF(I8="YES", COUNTIF($I$2:I8, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I8, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
         <v>4th</v>
       </c>
-      <c r="K8" s="18"/>
+      <c r="K8" s="15"/>
     </row>
     <row r="9" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="16">
+      <c r="A9" s="13">
         <f>MAX(A10:A$34) + 1</f>
         <v>25</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="G9" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="5" t="str">
-        <f>IF(I9="YES", COUNTIF($I$2:I9, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I9, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="J9" s="4" t="str">
+        <f>IF(I9="YES", COUNTIF($I$2:I9, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I9, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
         <v>5th</v>
       </c>
-      <c r="K9" s="18"/>
+      <c r="K9" s="15"/>
     </row>
     <row r="10" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="15">
+      <c r="A10" s="12">
         <f>MAX(A11:A$34) + 1</f>
         <v>24</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="I10" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="J10" s="9" t="str">
-        <f>IF(I10="YES", COUNTIF($I$2:I10, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I10, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="J10" s="8" t="str">
+        <f>IF(I10="YES", COUNTIF($I$2:I10, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I10, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
         <v>6th</v>
       </c>
-      <c r="K10" s="18"/>
+      <c r="K10" s="15"/>
     </row>
     <row r="11" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="16">
+      <c r="A11" s="13">
         <f>MAX(A12:A$34) + 1</f>
         <v>23</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="G11" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="I11" s="4"/>
-      <c r="J11" s="5" t="str">
-        <f>IF(I11="YES", COUNTIF($I$2:I11, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I11, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
-      </c>
-      <c r="K11" s="18"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="4" t="str">
+        <f>IF(I11="YES", COUNTIF($I$2:I11, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I11, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
+      </c>
+      <c r="K11" s="15"/>
     </row>
     <row r="12" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="15">
+      <c r="A12" s="12">
         <f>MAX(A13:A$34) + 1</f>
         <v>22</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="J12" s="9" t="str">
-        <f>IF(I12="YES", COUNTIF($I$2:I12, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I12, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="J12" s="8" t="str">
+        <f>IF(I12="YES", COUNTIF($I$2:I12, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I12, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
         <v>7th</v>
       </c>
-      <c r="K12" s="18"/>
+      <c r="K12" s="15"/>
     </row>
     <row r="13" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="16">
+      <c r="A13" s="13">
         <f>MAX(A14:A$34) + 1</f>
         <v>21</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="G13" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="I13" s="4"/>
-      <c r="J13" s="5" t="str">
-        <f>IF(I13="YES", COUNTIF($I$2:I13, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I13, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
-      </c>
-      <c r="K13" s="18"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="4" t="str">
+        <f>IF(I13="YES", COUNTIF($I$2:I13, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I13, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
+      </c>
+      <c r="K13" s="15"/>
     </row>
     <row r="14" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="15">
+      <c r="A14" s="12">
         <f>MAX(A15:A$34) + 1</f>
         <v>20</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="I14" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="J14" s="9" t="str">
-        <f>IF(I14="YES", COUNTIF($I$2:I14, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I14, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="J14" s="8" t="str">
+        <f>IF(I14="YES", COUNTIF($I$2:I14, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I14, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
         <v>8th</v>
       </c>
-      <c r="K14" s="18"/>
+      <c r="K14" s="15"/>
     </row>
     <row r="15" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="16">
+      <c r="A15" s="13">
         <f>MAX(A16:A$34) + 1</f>
         <v>19</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="G15" s="13" t="s">
+      <c r="G15" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="I15" s="4"/>
-      <c r="J15" s="5" t="str">
-        <f>IF(I15="YES", COUNTIF($I$2:I15, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I15, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
-      </c>
-      <c r="K15" s="18"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="4" t="str">
+        <f>IF(I15="YES", COUNTIF($I$2:I15, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I15, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
+      </c>
+      <c r="K15" s="15"/>
     </row>
     <row r="16" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="15">
+      <c r="A16" s="12">
         <f>MAX(A17:A$34) + 1</f>
         <v>18</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="H16" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="I16" s="8"/>
-      <c r="J16" s="9" t="str">
-        <f>IF(I16="YES", COUNTIF($I$2:I16, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I16, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
-      </c>
-      <c r="K16" s="18"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="8" t="str">
+        <f>IF(I16="YES", COUNTIF($I$2:I16, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I16, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
+      </c>
+      <c r="K16" s="15"/>
     </row>
     <row r="17" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="16">
+      <c r="A17" s="13">
         <f>MAX(A18:A$34) + 1</f>
         <v>17</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="G17" s="13" t="s">
+      <c r="G17" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="H17" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J17" s="5" t="str">
-        <f>IF(I17="YES", COUNTIF($I$2:I17, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I17, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
+      <c r="J17" s="4" t="str">
+        <f>IF(I17="YES", COUNTIF($I$2:I17, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I17, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
         <v>9th</v>
       </c>
-      <c r="K17" s="18"/>
+      <c r="K17" s="15"/>
     </row>
     <row r="18" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="15">
+      <c r="A18" s="12">
         <f>MAX(A19:A$34) + 1</f>
         <v>16</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="G18" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="H18" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="I18" s="8"/>
-      <c r="J18" s="9" t="str">
-        <f>IF(I18="YES", COUNTIF($I$2:I18, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I18, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
-      </c>
-      <c r="K18" s="18"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="8" t="str">
+        <f>IF(I18="YES", COUNTIF($I$2:I18, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I18, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
+      </c>
+      <c r="K18" s="15"/>
     </row>
     <row r="19" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="16">
+      <c r="A19" s="13">
         <f>MAX(A20:A$34) + 1</f>
         <v>15</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="G19" s="13" t="s">
+      <c r="G19" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="I19" s="4"/>
-      <c r="J19" s="5" t="str">
-        <f>IF(I19="YES", COUNTIF($I$2:I19, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I19, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
-      </c>
-      <c r="K19" s="18"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="4" t="str">
+        <f>IF(I19="YES", COUNTIF($I$2:I19, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I19, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
+      </c>
+      <c r="K19" s="15"/>
     </row>
     <row r="20" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="15">
+      <c r="A20" s="12">
         <f>MAX(A21:A$34) + 1</f>
         <v>14</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="G20" s="11" t="s">
+      <c r="G20" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="H20" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="I20" s="8"/>
-      <c r="J20" s="9" t="str">
-        <f>IF(I20="YES", COUNTIF($I$2:I20, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I20, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
-      </c>
-      <c r="K20" s="18"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="8" t="str">
+        <f>IF(I20="YES", COUNTIF($I$2:I20, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I20, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
+      </c>
+      <c r="K20" s="15"/>
     </row>
     <row r="21" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="16">
+      <c r="A21" s="13">
         <f>MAX(A22:A$34) + 1</f>
         <v>13</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="G21" s="13" t="s">
+      <c r="G21" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H21" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="I21" s="4"/>
-      <c r="J21" s="5" t="str">
-        <f>IF(I21="YES", COUNTIF($I$2:I21, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I21, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
-      </c>
-      <c r="K21" s="18"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="4" t="str">
+        <f>IF(I21="YES", COUNTIF($I$2:I21, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I21, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
+      </c>
+      <c r="K21" s="15"/>
     </row>
     <row r="22" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="15">
+      <c r="A22" s="12">
         <f>MAX(A23:A$34) + 1</f>
         <v>12</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="G22" s="11" t="s">
+      <c r="G22" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="H22" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="I22" s="8"/>
-      <c r="J22" s="9" t="str">
-        <f>IF(I22="YES", COUNTIF($I$2:I22, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I22, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
-      </c>
-      <c r="K22" s="18"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="8" t="str">
+        <f>IF(I22="YES", COUNTIF($I$2:I22, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I22, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
+      </c>
+      <c r="K22" s="15"/>
     </row>
     <row r="23" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="16">
+      <c r="A23" s="13">
         <f>MAX(A24:A$34) + 1</f>
         <v>11</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="G23" s="13" t="s">
+      <c r="G23" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="I23" s="4"/>
-      <c r="J23" s="5" t="str">
-        <f>IF(I23="YES", COUNTIF($I$2:I23, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I23, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
-      </c>
-      <c r="K23" s="18"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="4" t="str">
+        <f>IF(I23="YES", COUNTIF($I$2:I23, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I23, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
+      </c>
+      <c r="K23" s="15"/>
     </row>
     <row r="24" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="15">
+      <c r="A24" s="12">
         <f>MAX(A25:A$34) + 1</f>
         <v>10</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="G24" s="11" t="s">
+      <c r="G24" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="H24" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="I24" s="8"/>
-      <c r="J24" s="9" t="str">
-        <f>IF(I24="YES", COUNTIF($I$2:I24, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I24, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
-      </c>
-      <c r="K24" s="18"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="8" t="str">
+        <f>IF(I24="YES", COUNTIF($I$2:I24, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I24, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
+      </c>
+      <c r="K24" s="15"/>
     </row>
     <row r="25" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="16">
+      <c r="A25" s="13">
         <f>MAX(A26:A$34) + 1</f>
         <v>9</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="F25" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="G25" s="13" t="s">
+      <c r="G25" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="H25" s="4" t="s">
+      <c r="H25" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="I25" s="4"/>
-      <c r="J25" s="5" t="str">
-        <f>IF(I25="YES", COUNTIF($I$2:I25, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I25, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
-      </c>
-      <c r="K25" s="18"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="4" t="str">
+        <f>IF(I25="YES", COUNTIF($I$2:I25, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I25, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
+      </c>
+      <c r="K25" s="15"/>
     </row>
     <row r="26" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="15">
+      <c r="A26" s="12">
         <f>MAX(A27:A$34) + 1</f>
         <v>8</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="G26" s="11" t="s">
+      <c r="G26" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="H26" s="8" t="s">
+      <c r="H26" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="I26" s="8"/>
-      <c r="J26" s="9" t="str">
-        <f>IF(I26="YES", COUNTIF($I$2:I26, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I26, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
-      </c>
-      <c r="K26" s="18"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="8" t="str">
+        <f>IF(I26="YES", COUNTIF($I$2:I26, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I26, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
+      </c>
+      <c r="K26" s="15"/>
     </row>
     <row r="27" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="16">
+      <c r="A27" s="13">
         <f>MAX(A28:A$34) + 1</f>
         <v>7</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E27" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="F27" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="G27" s="13" t="s">
+      <c r="G27" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="H27" s="4" t="s">
+      <c r="H27" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="I27" s="4"/>
-      <c r="J27" s="5" t="str">
-        <f>IF(I27="YES", COUNTIF($I$2:I27, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I27, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
-      </c>
-      <c r="K27" s="18"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="4" t="str">
+        <f>IF(I27="YES", COUNTIF($I$2:I27, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I27, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
+      </c>
+      <c r="K27" s="15"/>
     </row>
     <row r="28" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="15">
+      <c r="A28" s="12">
         <f>MAX(A29:A$34) + 1</f>
         <v>6</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="G28" s="11" t="s">
+      <c r="G28" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="H28" s="8" t="s">
+      <c r="H28" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="I28" s="8"/>
-      <c r="J28" s="9" t="str">
-        <f>IF(I28="YES", COUNTIF($I$2:I28, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I28, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
-      </c>
-      <c r="K28" s="18"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="8" t="str">
+        <f>IF(I28="YES", COUNTIF($I$2:I28, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I28, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
+      </c>
+      <c r="K28" s="15"/>
     </row>
     <row r="29" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="16">
+      <c r="A29" s="13">
         <f>MAX(A30:A$34) + 1</f>
         <v>5</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F29" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="G29" s="13" t="s">
+      <c r="G29" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="H29" s="4" t="s">
+      <c r="H29" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="I29" s="4"/>
-      <c r="J29" s="5" t="str">
-        <f>IF(I29="YES", COUNTIF($I$2:I29, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I29, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
-      </c>
-      <c r="K29" s="18"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="4" t="str">
+        <f>IF(I29="YES", COUNTIF($I$2:I29, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I29, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
+      </c>
+      <c r="K29" s="15"/>
     </row>
     <row r="30" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="15">
+      <c r="A30" s="12">
         <f>MAX(A31:A$34) + 1</f>
         <v>4</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="D30" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="G30" s="11" t="s">
+      <c r="G30" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="H30" s="8" t="s">
+      <c r="H30" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="I30" s="8"/>
-      <c r="J30" s="9" t="str">
-        <f>IF(I30="YES", COUNTIF($I$2:I30, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I30, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
-      </c>
-      <c r="K30" s="18"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="8" t="str">
+        <f>IF(I30="YES", COUNTIF($I$2:I30, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I30, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
+      </c>
+      <c r="K30" s="15"/>
     </row>
     <row r="31" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="16">
+      <c r="A31" s="13">
         <f>MAX(A32:A$34) + 1</f>
         <v>3</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="E31" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="F31" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="G31" s="13" t="s">
+      <c r="G31" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="H31" s="4" t="s">
+      <c r="H31" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="I31" s="4"/>
-      <c r="J31" s="5" t="str">
-        <f>IF(I31="YES", COUNTIF($I$2:I31, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I31, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
-      </c>
-      <c r="K31" s="18"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="4" t="str">
+        <f>IF(I31="YES", COUNTIF($I$2:I31, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I31, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
+      </c>
+      <c r="K31" s="15"/>
     </row>
     <row r="32" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="15">
+      <c r="A32" s="12">
         <f>MAX(A33:A$34) + 1</f>
         <v>2</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D32" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E32" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="G32" s="11" t="s">
+      <c r="G32" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="H32" s="8" t="s">
+      <c r="H32" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="I32" s="8"/>
-      <c r="J32" s="9" t="str">
-        <f>IF(I32="YES", COUNTIF($I$2:I32, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I32, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
-      </c>
-      <c r="K32" s="18"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="8" t="str">
+        <f>IF(I32="YES", COUNTIF($I$2:I32, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I32, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
+      </c>
+      <c r="K32" s="15"/>
     </row>
     <row r="33" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="16">
+      <c r="A33" s="13">
         <f>MAX(A34:A$34) + 1</f>
         <v>1</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E33" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F33" s="3" t="s">
+      <c r="F33" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="G33" s="13" t="s">
+      <c r="G33" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="H33" s="4" t="s">
+      <c r="H33" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="I33" s="4"/>
-      <c r="J33" s="5" t="str">
-        <f>IF(I33="YES", COUNTIF($I$2:I33, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I33, "YES"), 4), "st", "nd", "rd", "th"), "")</f>
-        <v/>
-      </c>
-      <c r="K33" s="18"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="4" t="str">
+        <f>IF(I33="YES", COUNTIF($I$2:I33, "YES") &amp; CHOOSE(MIN(COUNTIF($I$2:I33, "YES"), 4), "st", "nd", "rd", "th"), "---")</f>
+        <v>---</v>
+      </c>
+      <c r="K33" s="15"/>
     </row>
     <row r="34" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="18"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
-      <c r="I34" s="18"/>
-      <c r="J34" s="18"/>
-      <c r="K34" s="18"/>
+      <c r="A34" s="15"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
+      <c r="J34" s="15"/>
+      <c r="K34" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/src/data/testimonials.xlsx
+++ b/src/data/testimonials.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\h2oontherock8\Projects\alexyaphomes\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83AE3091-9CB1-4728-88EC-82B66159C628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E16F40CB-0C42-41E6-B111-EE41E1FF29D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8460" yWindow="2710" windowWidth="30690" windowHeight="17510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8470" yWindow="2640" windowWidth="30000" windowHeight="17510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Testimonials" sheetId="1" r:id="rId1"/>
@@ -465,7 +465,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -527,6 +527,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -854,22 +857,22 @@
       <c r="A1" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="G1" s="22" t="s">
         <v>99</v>
       </c>
       <c r="H1" s="20" t="s">
